--- a/autotestgen/atg/test_cases/CS_RequirementDocument_Test_cases.xlsx
+++ b/autotestgen/atg/test_cases/CS_RequirementDocument_Test_cases.xlsx
@@ -477,22 +477,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Verify error message for incorrect username and correct password</t>
+          <t>Verify error message for invalid username and valid password</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Test that the application displays the correct error message when a user attempts to log in with an incorrect username but a correct password.</t>
+          <t>Test that the specified error message is displayed when an incorrect username is entered with a correct password during application login.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>['1. Navigate to the application login page.', "2. Enter an invalid username in the 'Username' field.", "3. Enter a valid password in the 'Password' field.", "4. Click the 'Login' button."]</t>
+          <t>['1. Navigate to the application login page.', '2. Enter an invalid username in the username field.', '3. Enter a valid password in the password field.', "4. Click the 'Login' button."]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The message "Invalid username or password. Please try again." is displayed on the screen.</t>
+          <t>The message 'Invalid username or password. Please try again.' is displayed on the login page.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -509,22 +509,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Verify error message for correct username and incorrect password</t>
+          <t>Verify error message for valid username and invalid password</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Test that the application displays the correct error message when a user attempts to log in with a correct username but an incorrect password.</t>
+          <t>Test that the specified error message is displayed when a correct username is entered with an incorrect password during application login.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>['1. Navigate to the application login page.', "2. Enter a valid username in the 'Username' field.", "3. Enter an invalid password in the 'Password' field.", "4. Click the 'Login' button."]</t>
+          <t>['1. Navigate to the application login page.', '2. Enter a valid username in the username field.', '3. Enter an invalid password in the password field.', "4. Click the 'Login' button."]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The message "Invalid username or password. Please try again." is displayed on the screen.</t>
+          <t>The message 'Invalid username or password. Please try again.' is displayed on the login page.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -541,22 +541,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Verify error message for both incorrect username and password</t>
+          <t>Verify error message for invalid username and invalid password</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Test that the application displays the correct error message when a user attempts to log in with both an incorrect username and an incorrect password.</t>
+          <t>Test that the specified error message is displayed when both username and password are incorrect during application login.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>['1. Navigate to the application login page.', "2. Enter an invalid username in the 'Username' field.", "3. Enter an invalid password in the 'Password' field.", "4. Click the 'Login' button."]</t>
+          <t>['1. Navigate to the application login page.', '2. Enter an invalid username in the username field.', '3. Enter an invalid password in the password field.', "4. Click the 'Login' button."]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>The message "Invalid username or password. Please try again." is displayed on the screen.</t>
+          <t>The message 'Invalid username or password. Please try again.' is displayed on the login page.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -573,22 +573,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Verify error message for empty username and empty password</t>
+          <t>Verify error message for empty username and valid password</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Test that the application displays the correct error message when a user attempts to log in with both username and password fields left empty.</t>
+          <t>Test that the specified error message is displayed when the username field is left empty and a valid password is provided.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>['1. Navigate to the application login page.', "2. Leave the 'Username' field empty.", "3. Leave the 'Password' field empty.", "4. Click the 'Login' button."]</t>
+          <t>['1. Navigate to the application login page.', '2. Leave the username field empty.', '3. Enter a valid password in the password field.', "4. Click the 'Login' button."]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The message "Invalid username or password. Please try again." is displayed on the screen.</t>
+          <t>The message 'Invalid username or password. Please try again.' is displayed on the login page.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -605,22 +605,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Verify error message for empty username and valid password</t>
+          <t>Verify error message for valid username and empty password</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Test that the application displays the correct error message when a user attempts to log in with an empty username and a valid password.</t>
+          <t>Test that the specified error message is displayed when a valid username is provided and the password field is left empty.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>['1. Navigate to the application login page.', "2. Leave the 'Username' field empty.", "3. Enter a valid password in the 'Password' field.", "4. Click the 'Login' button."]</t>
+          <t>['1. Navigate to the application login page.', '2. Enter a valid username in the username field.', '3. Leave the password field empty.', "4. Click the 'Login' button."]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The message "Invalid username or password. Please try again." is displayed on the screen.</t>
+          <t>The message 'Invalid username or password. Please try again.' is displayed on the login page.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -637,22 +637,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Verify 'Test Table' link visibility</t>
+          <t>Verify 'Test Table' link presence and clickability</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ensure that the new 'Test Table' link is visible on the designated page.</t>
+          <t>Test that the 'Test Table' link is present on the page and is clickable, leading to navigation.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>["1. Navigate to the page where the 'Test Table' link is expected to be added."]</t>
+          <t>["1. Navigate to the page where the 'Test Table' link is added.", "2. Locate the 'Test Table' link.", "3. Click on the 'Test Table' link."]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The 'Test Table' link is clearly visible on the page.</t>
+          <t>The 'Test Table' link is visible and clickable, and the user is navigated to the 'Test Table' screen/page.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -674,17 +674,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Test that clicking the 'Test Table' link successfully navigates the user to the 'Test Table' screen.</t>
+          <t>Test that clicking the 'Test Table' link successfully navigates the user to the intended 'Test Table' page with correct content.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>["1. Navigate to the page containing the 'Test Table' link.", "2. Click on the 'Test Table' link."]</t>
+          <t>["1. Navigate to the page containing the 'Test Table' link.", "2. Click the 'Test Table' link.", '3. Observe the URL and content of the navigated page.']</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>The application successfully navigates to the 'Test Table' screen/page.</t>
+          <t>The browser URL changes to the expected URL for the 'Test Table' page, and the page content corresponds to the 'Test Table' functionality.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -701,22 +701,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Verify 'Test Table' link is clickable</t>
+          <t>Verify 'Test Table' link styling and accessibility</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ensure that the 'Test Table' link is interactive and can be clicked by the user.</t>
+          <t>Test that the 'Test Table' link has appropriate styling (e.g., hover state, focus state) and is accessible via keyboard navigation.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>["1. Navigate to the page containing the 'Test Table' link.", "2. Attempt to click on the 'Test Table' link."]</t>
+          <t>["1. Navigate to the page where the 'Test Table' link is added.", "2. Hover the mouse over the 'Test Table' link and observe its appearance.", "3. Use keyboard navigation (e.g., Tab key) to focus on the 'Test Table' link and observe its appearance.", '4. Press Enter/Space when the link is focused.']</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>The 'Test Table' link is clickable and responds to the click action (e.g., cursor changes, link activates).</t>
+          <t>The link displays appropriate hover/focus styles. Pressing Enter/Space successfully navigates to the 'Test Table' page.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -733,27 +733,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Verify 'Test Table' link does not lead to broken page</t>
+          <t>Verify 'Test Table' link behavior for logged-out users (if applicable)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Confirm that the 'Test Table' link does not lead to a 404 error or any other broken page.</t>
+          <t>Test if the 'Test Table' link is visible and functional for users who are not logged in, or if it redirects to a login page as expected.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>["1. Navigate to the page containing the 'Test Table' link.", "2. Click on the 'Test Table' link."]</t>
+          <t>['1. Ensure the user is logged out of the application.', "2. Navigate to the page where the 'Test Table' link is expected.", "3. Locate and click the 'Test Table' link."]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The application navigates to a valid page without displaying any error messages (e.g., 404 Not Found, Server Error).</t>
+          <t>The link is either not visible, or it is visible but redirects to a login page, or it allows access to public 'Test Table' content, as per design specifications for logged-out users.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -765,27 +765,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Verify 'Test Table' link text and styling</t>
+          <t>Verify 'Test Table' link does not lead to a broken page</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Check that the 'Test Table' link displays the correct text and adheres to the application's styling guidelines.</t>
+          <t>Test that clicking the 'Test Table' link does not result in a 404, 500, or any other error page.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>["1. Navigate to the page containing the 'Test Table' link."]</t>
+          <t>["1. Navigate to the page containing the 'Test Table' link.", "2. Click the 'Test Table' link.", '3. Observe the navigated page for any HTTP error codes or application-level error messages.']</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The link text is exactly "Test Table" and its styling (e.g., color, font, underline) is consistent with other links in the application.</t>
+          <t>The navigated page loads successfully without any HTTP error codes (e.g., 404, 500) or application-level error messages.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
     </row>
@@ -797,22 +797,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Verify 'Java' option is displayed as a radio button</t>
+          <t>Verify 'Java' element is a radio button</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Confirm that the UI element for 'Java' on the 'Test Table' screen has been changed from a checkbox to a radio button.</t>
+          <t>Test that the element associated with the label 'Java' on the 'Test Table' screen is correctly rendered as a radio button.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>["1. Navigate to the 'Test Table' screen."]</t>
+          <t>["1. Navigate to the 'Test Table' screen.", "2. Locate the element labeled 'Java'.", "3. Visually inspect the element's type or use browser developer tools to confirm its HTML input type."]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The option labeled 'Java' is displayed as a radio button.</t>
+          <t>The element labeled 'Java' is displayed as a radio button (input type='radio').</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -829,22 +829,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Verify 'Java' radio button is selectable</t>
+          <t>Verify 'Java' radio button can be selected</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ensure that the 'Java' radio button can be selected by the user.</t>
+          <t>Test that the 'Java' radio button can be successfully selected by clicking it.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>["1. Navigate to the 'Test Table' screen.", "2. Click on the 'Java' radio button."]</t>
+          <t>["1. Navigate to the 'Test Table' screen.", "2. Locate the 'Java' radio button.", "3. Click on the 'Java' radio button."]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>The 'Java' radio button becomes selected (e.g., filled in).</t>
+          <t>The 'Java' radio button becomes selected (checked) after clicking.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -861,22 +861,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Verify selecting 'Java' deselects other radio buttons in its group</t>
+          <t>Verify 'Java' radio button's mutual exclusivity</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Test that when 'Java' radio button is selected, any other previously selected radio button within the same group is deselected.</t>
+          <t>Test that selecting 'Java' deselects any other radio button in the same group, and selecting another radio button deselects 'Java', demonstrating mutual exclusivity.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>["1. Navigate to the 'Test Table' screen.", "2. Select another radio button (e.g., 'C#') in the same group as 'Java'.", "3. Click on the 'Java' radio button."]</t>
+          <t>["1. Navigate to the 'Test Table' screen.", "2. Select the 'Java' radio button.", "3. Select another radio button (e.g., 'Python', 'C#') from the same group.", "4. Observe the state of the 'Java' radio button and the newly selected radio button."]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>The 'Java' radio button is selected, and the previously selected radio button ('C#') is deselected.</t>
+          <t>When another radio button in the same group is selected, the 'Java' radio button becomes deselected, and vice-versa. Only one radio button in the group can be selected at a time.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -893,22 +893,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Verify the label 'Java' is correctly associated with the radio button</t>
+          <t>Verify 'Java' radio button initial state on page load</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ensure that clicking on the 'Java' label also selects the corresponding radio button.</t>
+          <t>Test the default selected state of the 'Java' radio button when the 'Test Table' screen initially loads.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>["1. Navigate to the 'Test Table' screen.", '2. Click on the text label "Java" next to the radio button.']</t>
+          <t>["1. Navigate to the 'Test Table' screen.", "2. Observe the initial state (selected/unselected) of the 'Java' radio button upon page load."]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The 'Java' radio button becomes selected.</t>
+          <t>The 'Java' radio button is unselected by default, or it is pre-selected if there is a specific requirement for its initial state.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -925,27 +925,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Verify the previous 'Java' checkbox is no longer present</t>
+          <t>Verify no checkbox exists for 'Java'</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Confirm that the old 'Java' checkbox element has been completely removed from the 'Test Table' screen.</t>
+          <t>Test that there is no checkbox element associated with the label 'Java' on the 'Test Table' screen, confirming the change from checkbox to radio button.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>["1. Navigate to the 'Test Table' screen.", "2. Visually inspect the area where the 'Java' checkbox was previously located."]</t>
+          <t>["1. Navigate to the 'Test Table' screen.", "2. Visually scan the elements near the 'Java' label.", "3. Use browser developer tools to inspect elements and confirm no input type='checkbox' is present for 'Java'."]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>The 'Java' checkbox is not present on the screen; only the 'Java' radio button is visible.</t>
+          <t>No checkbox element is found for the label 'Java'. Only a radio button is present.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
     </row>

--- a/autotestgen/atg/test_cases/CS_RequirementDocument_Test_cases.xlsx
+++ b/autotestgen/atg/test_cases/CS_RequirementDocument_Test_cases.xlsx
@@ -472,27 +472,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TC-CR1-001</t>
+          <t>TC-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Verify error message for invalid username and valid password</t>
+          <t>Login with Valid Username and Invalid Password</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Test that the specified error message is displayed when an incorrect username is entered with a correct password during application login.</t>
+          <t>Verify the error message when a user attempts to log in with a correct username but an incorrect password.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>['1. Navigate to the application login page.', '2. Enter an invalid username in the username field.', '3. Enter a valid password in the password field.', "4. Click the 'Login' button."]</t>
+          <t>['Navigate to the application login page.', "Enter a valid username in the 'Username' field.", "Enter an invalid password in the 'Password' field.", "Click the 'Login' button."]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The message 'Invalid username or password. Please try again.' is displayed on the login page.</t>
+          <t>The message 'Invalid username or password. Please try again.' is displayed on the screen.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -504,27 +504,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TC-CR1-002</t>
+          <t>TC-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Verify error message for valid username and invalid password</t>
+          <t>Login with Invalid Username and Valid Password</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Test that the specified error message is displayed when a correct username is entered with an incorrect password during application login.</t>
+          <t>Verify the error message when a user attempts to log in with an incorrect username but a correct password.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>['1. Navigate to the application login page.', '2. Enter a valid username in the username field.', '3. Enter an invalid password in the password field.', "4. Click the 'Login' button."]</t>
+          <t>['Navigate to the application login page.', "Enter an invalid username in the 'Username' field.", "Enter a valid password in the 'Password' field.", "Click the 'Login' button."]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The message 'Invalid username or password. Please try again.' is displayed on the login page.</t>
+          <t>The message 'Invalid username or password. Please try again.' is displayed on the screen.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -536,27 +536,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TC-CR1-003</t>
+          <t>TC-003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Verify error message for invalid username and invalid password</t>
+          <t>Login with Invalid Username and Invalid Password</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Test that the specified error message is displayed when both username and password are incorrect during application login.</t>
+          <t>Verify the error message when a user attempts to log in with both incorrect username and password.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>['1. Navigate to the application login page.', '2. Enter an invalid username in the username field.', '3. Enter an invalid password in the password field.', "4. Click the 'Login' button."]</t>
+          <t>['Navigate to the application login page.', "Enter an invalid username in the 'Username' field.", "Enter an invalid password in the 'Password' field.", "Click the 'Login' button."]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>The message 'Invalid username or password. Please try again.' is displayed on the login page.</t>
+          <t>The message 'Invalid username or password. Please try again.' is displayed on the screen.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -568,27 +568,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TC-CR1-004</t>
+          <t>TC-004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Verify error message for empty username and valid password</t>
+          <t>Login with Empty Username and Valid Password</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Test that the specified error message is displayed when the username field is left empty and a valid password is provided.</t>
+          <t>Verify the error message when a user attempts to log in with an empty username and a valid password.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>['1. Navigate to the application login page.', '2. Leave the username field empty.', '3. Enter a valid password in the password field.', "4. Click the 'Login' button."]</t>
+          <t>['Navigate to the application login page.', "Leave the 'Username' field empty.", "Enter a valid password in the 'Password' field.", "Click the 'Login' button."]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The message 'Invalid username or password. Please try again.' is displayed on the login page.</t>
+          <t>The message 'Invalid username or password. Please try again.' is displayed on the screen.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -600,27 +600,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TC-CR1-005</t>
+          <t>TC-005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Verify error message for valid username and empty password</t>
+          <t>Login with Valid Username and Empty Password</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Test that the specified error message is displayed when a valid username is provided and the password field is left empty.</t>
+          <t>Verify the error message when a user attempts to log in with a valid username and an empty password.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>['1. Navigate to the application login page.', '2. Enter a valid username in the username field.', '3. Leave the password field empty.', "4. Click the 'Login' button."]</t>
+          <t>['Navigate to the application login page.', "Enter a valid username in the 'Username' field.", "Leave the 'Password' field empty.", "Click the 'Login' button."]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The message 'Invalid username or password. Please try again.' is displayed on the login page.</t>
+          <t>The message 'Invalid username or password. Please try again.' is displayed on the screen.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -632,27 +632,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TC-CR2-001</t>
+          <t>TC-006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Verify 'Test Table' link presence and clickability</t>
+          <t>Verify 'Test Table' link presence</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Test that the 'Test Table' link is present on the page and is clickable, leading to navigation.</t>
+          <t>Confirm that the new 'Test Table' link is visible on the page.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>["1. Navigate to the page where the 'Test Table' link is added.", "2. Locate the 'Test Table' link.", "3. Click on the 'Test Table' link."]</t>
+          <t>["Navigate to the page where the 'Test Table' link is expected to be added.", 'Visually inspect the page.']</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The 'Test Table' link is visible and clickable, and the user is navigated to the 'Test Table' screen/page.</t>
+          <t>The 'Test Table' link is clearly visible and accessible on the page.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -664,27 +664,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TC-CR2-002</t>
+          <t>TC-007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Verify 'Test Table' link navigates to the correct page</t>
+          <t>Verify 'Test Table' link navigation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Test that clicking the 'Test Table' link successfully navigates the user to the intended 'Test Table' page with correct content.</t>
+          <t>Confirm that clicking the 'Test Table' link successfully navigates the user to the 'Test Table' screen.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>["1. Navigate to the page containing the 'Test Table' link.", "2. Click the 'Test Table' link.", '3. Observe the URL and content of the navigated page.']</t>
+          <t>["Navigate to the page containing the 'Test Table' link.", "Click on the 'Test Table' link."]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>The browser URL changes to the expected URL for the 'Test Table' page, and the page content corresponds to the 'Test Table' functionality.</t>
+          <t>The application navigates to the 'Test Table' screen/page. The URL should reflect the 'Test Table' page, and its content should be displayed.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -696,27 +696,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TC-CR2-003</t>
+          <t>TC-008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Verify 'Test Table' link styling and accessibility</t>
+          <t>Verify 'Test Table' link functionality (back navigation)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Test that the 'Test Table' link has appropriate styling (e.g., hover state, focus state) and is accessible via keyboard navigation.</t>
+          <t>Confirm that after navigating to the 'Test Table' screen, the user can return to the previous page using the browser's back functionality.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>["1. Navigate to the page where the 'Test Table' link is added.", "2. Hover the mouse over the 'Test Table' link and observe its appearance.", "3. Use keyboard navigation (e.g., Tab key) to focus on the 'Test Table' link and observe its appearance.", '4. Press Enter/Space when the link is focused.']</t>
+          <t>["Navigate to the page containing the 'Test Table' link.", "Click on the 'Test Table' link to go to the 'Test Table' screen.", "Use the browser's 'Back' button."]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>The link displays appropriate hover/focus styles. Pressing Enter/Space successfully navigates to the 'Test Table' page.</t>
+          <t>The user is successfully navigated back to the page from which the 'Test Table' link was clicked.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -728,91 +728,91 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TC-CR2-004</t>
+          <t>TC-009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Verify 'Test Table' link behavior for logged-out users (if applicable)</t>
+          <t>Verify 'Test Table' link attributes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Test if the 'Test Table' link is visible and functional for users who are not logged in, or if it redirects to a login page as expected.</t>
+          <t>Check if the 'Test Table' link opens in the same window/tab and has basic accessibility attributes.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>['1. Ensure the user is logged out of the application.', "2. Navigate to the page where the 'Test Table' link is expected.", "3. Locate and click the 'Test Table' link."]</t>
+          <t>["Navigate to the page containing the 'Test Table' link.", "Inspect the HTML attributes of the 'Test Table' link (e.g., 'target', 'href', 'aria-label' if applicable)."]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The link is either not visible, or it is visible but redirects to a login page, or it allows access to public 'Test Table' content, as per design specifications for logged-out users.</t>
+          <t>The link's 'target' attribute is '_self' (or not present, implying '_self'). The 'href' attribute points to the correct 'Test Table' URL.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TC-CR2-005</t>
+          <t>TC-010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Verify 'Test Table' link does not lead to a broken page</t>
+          <t>Verify 'Test Table' link behavior on right-click</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Test that clicking the 'Test Table' link does not result in a 404, 500, or any other error page.</t>
+          <t>Verify standard browser context menu options are available for the 'Test Table' link.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>["1. Navigate to the page containing the 'Test Table' link.", "2. Click the 'Test Table' link.", '3. Observe the navigated page for any HTTP error codes or application-level error messages.']</t>
+          <t>["Navigate to the page containing the 'Test Table' link.", "Right-click on the 'Test Table' link."]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The navigated page loads successfully without any HTTP error codes (e.g., 404, 500) or application-level error messages.</t>
+          <t>The browser's context menu appears with options like 'Open link in new tab', 'Copy link address', etc.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TC-CR3-001</t>
+          <t>TC-011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Verify 'Java' element is a radio button</t>
+          <t>Verify 'Java' element type is Radio Button</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Test that the element associated with the label 'Java' on the 'Test Table' screen is correctly rendered as a radio button.</t>
+          <t>Confirm that the element associated with the label 'Java' on the 'Test Table' screen is a radio button.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>["1. Navigate to the 'Test Table' screen.", "2. Locate the element labeled 'Java'.", "3. Visually inspect the element's type or use browser developer tools to confirm its HTML input type."]</t>
+          <t>["Navigate to the 'Test Table' screen.", "Locate the element labeled 'Java'.", "Inspect the element's type."]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The element labeled 'Java' is displayed as a radio button (input type='radio').</t>
+          <t>The element labeled 'Java' is rendered as a radio button (&lt;input type="radio"&gt;).</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -824,27 +824,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TC-CR3-002</t>
+          <t>TC-012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Verify 'Java' radio button can be selected</t>
+          <t>Verify 'Java' radio button selection functionality</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Test that the 'Java' radio button can be successfully selected by clicking it.</t>
+          <t>Confirm that the 'Java' radio button can be selected.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>["1. Navigate to the 'Test Table' screen.", "2. Locate the 'Java' radio button.", "3. Click on the 'Java' radio button."]</t>
+          <t>["Navigate to the 'Test Table' screen.", "Click on the 'Java' radio button."]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>The 'Java' radio button becomes selected (checked) after clicking.</t>
+          <t>The 'Java' radio button becomes selected (checked).</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -856,27 +856,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TC-CR3-003</t>
+          <t>TC-013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Verify 'Java' radio button's mutual exclusivity</t>
+          <t>Verify 'Java' radio button exclusivity within its group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Test that selecting 'Java' deselects any other radio button in the same group, and selecting another radio button deselects 'Java', demonstrating mutual exclusivity.</t>
+          <t>Confirm that selecting another radio button in the same group deselects the 'Java' radio button.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>["1. Navigate to the 'Test Table' screen.", "2. Select the 'Java' radio button.", "3. Select another radio button (e.g., 'Python', 'C#') from the same group.", "4. Observe the state of the 'Java' radio button and the newly selected radio button."]</t>
+          <t>["Navigate to the 'Test Table' screen.", "Click on the 'Java' radio button to select it.", "Click on another radio button (e.g., 'Python', 'C#') that belongs to the same group as 'Java'."]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>When another radio button in the same group is selected, the 'Java' radio button becomes deselected, and vice-versa. Only one radio button in the group can be selected at a time.</t>
+          <t>The 'Java' radio button is deselected, and the newly clicked radio button is selected.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -888,27 +888,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TC-CR3-004</t>
+          <t>TC-014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Verify 'Java' radio button initial state on page load</t>
+          <t>Verify 'Java' radio button initial state</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Test the default selected state of the 'Java' radio button when the 'Test Table' screen initially loads.</t>
+          <t>Confirm that the 'Java' radio button is initially unselected when the 'Test Table' screen loads.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>["1. Navigate to the 'Test Table' screen.", "2. Observe the initial state (selected/unselected) of the 'Java' radio button upon page load."]</t>
+          <t>["Navigate to the 'Test Table' screen.", "Observe the state of the 'Java' radio button."]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The 'Java' radio button is unselected by default, or it is pre-selected if there is a specific requirement for its initial state.</t>
+          <t>The 'Java' radio button is initially unselected (unchecked).</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -920,32 +920,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TC-CR3-005</t>
+          <t>TC-015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Verify no checkbox exists for 'Java'</t>
+          <t>Verify absence of 'Java' checkbox</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Test that there is no checkbox element associated with the label 'Java' on the 'Test Table' screen, confirming the change from checkbox to radio button.</t>
+          <t>Confirm that no checkbox element with the label 'Java' is present on the 'Test Table' screen.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>["1. Navigate to the 'Test Table' screen.", "2. Visually scan the elements near the 'Java' label.", "3. Use browser developer tools to inspect elements and confirm no input type='checkbox' is present for 'Java'."]</t>
+          <t>["Navigate to the 'Test Table' screen.", "Visually inspect the screen for any checkbox labeled 'Java'.", '(Optional) Inspect the DOM for &lt;input type="checkbox"&gt; elements associated with \'Java\'.']</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>No checkbox element is found for the label 'Java'. Only a radio button is present.</t>
+          <t>No checkbox element labeled 'Java' is found on the 'Test Table' screen.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
